--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130584972</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130584972</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130584972</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130584972</v>
       </c>
       <c r="B2" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130584972</v>
       </c>
       <c r="B2" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130584972</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>130584972</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -778,6 +778,427 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97430405</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5173</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Myskbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aromia moschata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Morgongåva, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>608361</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6647290</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-11-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-11-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130584973</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>105076</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sinodendron cylindricum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Morgongåva, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608360</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6647258</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>gnag i sälg</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130584947</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Morgongåva, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608377</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6647264</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130584970</v>
+      </c>
+      <c r="B6" t="n">
+        <v>40269</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>214815</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Större träfjäril</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cossus cossus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Morgongåva, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608362</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6647283</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>gnag i sälg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58369-2025 artfynd.xlsx
+++ b/artfynd/A 58369-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130584972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97430405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130584973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130584947</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,8 +1224,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130584970</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>